--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,210 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RoadSync</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f605a11b0b8a05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sr Associate Data Analytics</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbfe0f5be436a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cloud AI Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ericsson</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56d6c36863f4059e</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0872ac97637e8ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>machine learning and LLM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>suburban imaging</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ffbd42704f90bb1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Marketing Data Scientist</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Puget Sound Energy</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3fffc8ec6454fd</t>
+          <t>https://www.indeed.com/viewjob?jk=96e6e5ae8e575f10</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,245 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Orbis AI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80ad300443dda3e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior ML/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Catapult Sports</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, EC2, Data Lake, Kinesis, Git, Kafka, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Orbis AI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1f205cb3b26b005</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeb516bb9fc8564b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Orbis AI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09e43b7607a681c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer III (US)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mount Laurel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Kafka, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96e6e5ae8e575f10</t>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4229cd2b126cc88</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>AI / ML Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Orbis AI</t>
+          <t>Vortalsoft usa.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ad300443dda3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=11b76c169c068558</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Remote, US)</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL, Python</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2f39f3379fbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Data Engineer (6278)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, EC2, Data Lake, Kinesis, Git, Kafka, MongoDB, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=22ea4a61a03aa31b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orbis AI</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f205cb3b26b005</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,77 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb516bb9fc8564b</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Orbis AI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09e43b7607a681c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer III (US)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Kafka, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4229cd2b126cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI / ML Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vortalsoft usa.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b76c169c068558</t>
+          <t>https://www.indeed.com/viewjob?jk=bac725c816b7cca6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Data Scientist - San Juan, PR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=87de4d13401c87d1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (6278)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Waste Connections</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>The Woodlands, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>Data Scientist, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ea4a61a03aa31b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7f96c7cbb10552</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>STORD Warehouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=cde9b530eec99876</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Synapse, Data Lake, CI/CD, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Apache Airflow, CI/CD, Git, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac725c816b7cca6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4a24f7d4b2f1f5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist - San Juan, PR</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Databricks, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87de4d13401c87d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce77873e849b4e2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Waste Connections</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Woodlands, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Databricks, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7f96c7cbb10552</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>STORD Warehouse</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,532 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde9b530eec99876</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f76c838cdf5a93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, FastAPI, Docker, Terraform, Databricks, PySpark, Kafka, Hadoop</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Woongjin, Inc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer - Azure</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b1dd7fbd77be6e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Emed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Insperity</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kingwood, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, Snowflake, Databricks, Redshift, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01b41195ed79eac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, CI/CD, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr AI Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Omega Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, S3, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bc297f6e43356b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b6d9ab8de67501f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ONTIC TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, Synapse, Data Lake, CI/CD, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af3adeb5b45473ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer I</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Insperity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kingwood, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b59d3e3c3ac3e2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI app builder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Morrell International</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=253fbf5e027b0ce6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Operations Scientist, Development</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4a24f7d4b2f1f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist, Finance Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United States Steel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Data Scientist, Generative AI, LangChain, Copilot, TensorFlow, PyTorch, MLflow, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce77873e849b4e2</t>
+          <t>https://www.indeed.com/viewjob?jk=fc239aef4b02847e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Application Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>Generative AI, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=f16c01d9addff559</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f76c838cdf5a93</t>
+          <t>https://www.indeed.com/viewjob?jk=1640808e3ec270e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FastAPI, Docker, Terraform, Databricks, PySpark, Kafka, Hadoop</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=072de349e77927c3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c0e1b087627115</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, Terraform, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer, ROR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1dd7fbd77be6e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a74eecfd78cc78a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Applied AI Engineer Intern / Basketball Operations</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Athena, Redshift, Redshift, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2fd260c4fe3e90</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Accel Entertainment Gaming, LLC.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Burr Ridge, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0454f719bec244</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Accel Entertainment Gaming, LLC.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, Snowflake, Databricks, Redshift, Hadoop, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=12e1202b02b04768</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Security Platform Engineer - MTS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b41195ed79eac3</t>
+          <t>https://www.indeed.com/viewjob?jk=deffb6949c95207d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, CI/CD, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Cortex, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr AI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Omega Solutions Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, S3, CI/CD, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc297f6e43356b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a1ce76ef7125a9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e168a5151557b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6d9ab8de67501f</t>
+          <t>https://www.indeed.com/viewjob?jk=434115e7508452c1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ONTIC TECHNOLOGIES</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>Redshift, Docker, Kubernetes, Snowflake, Databricks, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af3adeb5b45473ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer I</t>
+          <t>UI Desktop Engineer Hybird</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b59d3e3c3ac3e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=1617b1c710a6c07a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI app builder</t>
+          <t>Senior Full-Stack Engineer — AI Agent Systems</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Morrell International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253fbf5e027b0ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=2793568770a31ec4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr BI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=084535632520342a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-17.xlsx
+++ b/daily_matches/job_matches_2026-08-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Operations Scientist, Development</t>
+          <t>Engineer Software (Prisma AIRS Backend)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Synapse, MLflow</t>
+          <t>BigQuery, Docker, Kubernetes, AKS, CI/CD, Git, BigQuery, Kafka, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=b7af7958a7b7c98c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Finance Analytics</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United States Steel</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Copilot, TensorFlow, PyTorch, MLflow, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, BigQuery, Git, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc239aef4b02847e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Application Reliability Engineer</t>
+          <t>Builder (Software Development Engineer) | Xome</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, CI/CD, Git, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16c01d9addff559</t>
+          <t>https://www.indeed.com/viewjob?jk=8129f5aa4013276f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ivy Rehab Network</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1640808e3ec270e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0eda356cadbab6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, Snowflake, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072de349e77927c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solutions Architect, Financial Services Banking</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, MongoDB, Cassandra, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Git, Dask, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c0e1b087627115</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4094dfd463872b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Echo Consulting Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, Terraform, BigQuery, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=c435c4fae9ab59dc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, ROR</t>
+          <t>Full-Stack PHP Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>America's Best House Plans</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marietta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL</t>
+          <t>RAG, Prompt Engineering, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a74eecfd78cc78a</t>
+          <t>https://www.indeed.com/viewjob?jk=5334ef034bac7ab1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applied AI Engineer Intern / Basketball Operations</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oklahoma City Thunder</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Athena, Redshift, Redshift, Python</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, Kubernetes, Git, Kafka, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2fd260c4fe3e90</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4b34fa0a9504e7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burr Ridge, IL, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0454f719bec244</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accel Entertainment Gaming, LLC.</t>
+          <t>NetSPI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Data Lake, CI/CD, Databricks, Python, SQL</t>
+          <t>S3, Docker, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e1202b02b04768</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa161d158387111</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Security Platform Engineer - MTS</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deffb6949c95207d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>LLM Engineer (Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Cortex, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a35624d7ae7f8a38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a1ce76ef7125a9</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Volaris Group Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e168a5151557b7</t>
+          <t>https://www.indeed.com/viewjob?jk=698c40272b6b8a1d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior AI/ML Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434115e7508452c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c79d5d098464789e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer IV, Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, Docker, Kubernetes, Snowflake, Databricks, Redshift, Python, SQL, R, Scala</t>
+          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8c846c7ee0ad44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UI Desktop Engineer Hybird</t>
+          <t>Software Engineer IV, Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1617b1c710a6c07a</t>
+          <t>https://www.indeed.com/viewjob?jk=50ccd94d68607909</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer — AI Agent Systems</t>
+          <t>DevOps / ML-Ops Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DeepSig Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, Docker, CI/CD, Git, PostgreSQL, SQL, R</t>
+          <t>RAG, MLflow, Docker, CI/CD, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2793568770a31ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=835bba6a95087086</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,287 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084535632520342a</t>
+          <t>https://www.indeed.com/viewjob?jk=482eb850bacc9bd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, CI/CD, Databricks, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f625bf42dc6dd62f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Insights &amp; Analytics Senior Specialist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4420218f2887f1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54935cf92419b836</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ontic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7b6900ab8d1a1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>First Advantage</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b021054365599b9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IPT Global</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Keras, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a100bd1f16487c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e71a64168becbf0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C# Developer Intern</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Scalp Trade LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b844f3d54a54748</t>
         </is>
       </c>
     </row>
